--- a/data/2026-04-13/SCW Weekly Comp 2026-04-13 (Responses).xlsx
+++ b/data/2026-04-13/SCW Weekly Comp 2026-04-13 (Responses).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="344">
   <si>
     <t>Timestamp</t>
   </si>
@@ -968,6 +968,81 @@
   </si>
   <si>
     <t>https://www.facebook.com/events/1309623684420996/permalink/1319878783395486/?app=fbl</t>
+  </si>
+  <si>
+    <t>Danielle Kay</t>
+  </si>
+  <si>
+    <t>2023KAYD01</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/1317286277261086/?post_id=1326422963014084&amp;view=permalink&amp;__cft__[0]=AZaEJhsuy0dbfMGbxLdeSTwZcVSF6xPcxwLtnfWhsTh60WNDIxzodusRV8iUGTPrnmfj-b2FDxd_4Qzx28sdguMIy-3RaMJMM7Jyspuh9E-3PcEZUicDGEK-p6-E_Jfx73I&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/1309623684420996/?post_id=1318060730243958&amp;view=permalink&amp;__cft__[0]=AZZRf6k5NfQF5NSPGRdi3sg2oGj3tO_LxkvBu5XXPcD_TNvGj55x43ad1rnht8OhBlALgcHdqC6hrsJyLzia_pa3O9MxjXl_KbDIm2TsZecXsFhpCr9fKRZb0FEllYGOjKg&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/1309623684420996/?post_id=1318087666907931&amp;view=permalink&amp;__cft__[0]=AZZG7VDOuPzLqxqXbzHYcSuDYB2ODE11Aw4LCaDKuAP9_AzmEGEazXsTTWwSZ_gxRfZkUCtJrQEwHk03qcXw84HWGGEKuUDQN-gZdUBEJXz8fQyPfdi8TsuIPNoaltu-zSs&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/1309623684420996/?post_id=1318101936906504&amp;view=permalink&amp;__cft__[0]=AZYG0i06srz6Vgj-AuEkV_UvrxwBeQrXQhmQxwNmgxNiHF7FYR3sb0VMNCvX-cSMmT78gaBKO322go5-qJnTGbbs5QYx3GAc_2G3LyWkWOB0sZdj0qyrGHBLvLEngUR6UoU&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/1317286277261086/?post_id=1326504356339278&amp;view=permalink&amp;__cft__[0]=AZaBKg1gjiau9mnRiUjjtaSGQtJJP3eRls8CswnVpaAdQkPJmpxnoUTilQnGuq0_nPS-OJkwDfXjw9N3IIACzNskWPqOfGpH4DiFAnLOxAk2BrZAQy5WP5FjbJeuafWl2-I&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/1317286277261086/?post_id=1326523499670697&amp;view=permalink&amp;__cft__[0]=AZZNFGGnaRlcifoE8YlQrrGC0mLtwimxwjrMtVuJHFZ17yQaCYUIbfpruDU69bFs7u7IEDwjJxWlgt8rh722_K82dZtg7cdoKkm5EnZ96UC8WcysqEowzdOOqQn2s8X2PNU&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/966012039140622/?post_id=974625454945947&amp;view=permalink&amp;__cft__[0]=AZbt5AKS4e_TKtn-iSLNOW3EiGHx_XAoiTxJ33nj74-FTV_b34JOBzsZ59Rqke8fW6t7Upg0JeEHTE0p8r1Yfc5BVuRQB6t3BocbzUUMeODrD8bLVUZYwgDrt0WQH8pAg04&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>1:38.06</t>
+  </si>
+  <si>
+    <t>1:41.91</t>
+  </si>
+  <si>
+    <t>1:32.44</t>
+  </si>
+  <si>
+    <t>1:37.47</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/966012039140622/?post_id=974649804943512&amp;view=permalink&amp;__cft__[0]=AZbCFuBnmA62dv9-fkqeDgzdKNCaVfigwCf76yM_8S3UcqL23_Pauel0YEY0wSaK4bXKtQgBxnT8KMdqjcGUtoGsD0Q8oXXKloI6_jb7Vzn3tx1J-YoSU9paWWl_340tYJQ&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>2:40.46</t>
+  </si>
+  <si>
+    <t>2:38.46</t>
+  </si>
+  <si>
+    <t>2:42.37</t>
+  </si>
+  <si>
+    <t>2:40.43</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/1309623684420996/?post_id=1318929990157032&amp;view=permalink&amp;__cft__[0]=AZaKGVvHfI4Ep4Li36_WBZ2IPLWVW74lqzxxBuUGZUqJlBiT0FvwY9CMOvZBLQuMVZqWaFZiEHaRLHLbG8Al_IBEvPpXmBJqAYeO43cIcARvxFSDDruIqnL444wwtGSBqZM&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>2:00.22</t>
+  </si>
+  <si>
+    <t>2:16.79</t>
+  </si>
+  <si>
+    <t>2:03.38</t>
+  </si>
+  <si>
+    <t>1:56.99</t>
+  </si>
+  <si>
+    <t>2:04.53</t>
+  </si>
+  <si>
+    <t>2:02.71</t>
   </si>
 </sst>
 </file>
@@ -977,7 +1052,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1004,22 +1079,183 @@
       <color rgb="FF434343"/>
       <name val="Roboto"/>
     </font>
+    <font>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor rgb="FFF8F9FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="29">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1053,6 +1289,48 @@
     <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="3" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="2" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="2" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1112,12 +1390,16 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="1">
+  <tableStyles count="2">
     <tableStyle count="4" pivot="0" name="Form responses 1-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+    <tableStyle count="2" pivot="0" name="Form responses 1-style 2">
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -1248,6 +1530,126 @@
     <tableColumn name="Time" id="112"/>
   </tableColumns>
   <tableStyleInfo name="Form responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A56:DH64" displayName="Table_1" name="Table_1" id="2">
+  <tableColumns count="112">
+    <tableColumn name="Column1" id="1"/>
+    <tableColumn name="Column2" id="2"/>
+    <tableColumn name="Column3" id="3"/>
+    <tableColumn name="Column4" id="4"/>
+    <tableColumn name="Column5" id="5"/>
+    <tableColumn name="Column6" id="6"/>
+    <tableColumn name="Column7" id="7"/>
+    <tableColumn name="Column8" id="8"/>
+    <tableColumn name="Column9" id="9"/>
+    <tableColumn name="Column10" id="10"/>
+    <tableColumn name="Column11" id="11"/>
+    <tableColumn name="Column12" id="12"/>
+    <tableColumn name="Column13" id="13"/>
+    <tableColumn name="Column14" id="14"/>
+    <tableColumn name="Column15" id="15"/>
+    <tableColumn name="Column16" id="16"/>
+    <tableColumn name="Column17" id="17"/>
+    <tableColumn name="Column18" id="18"/>
+    <tableColumn name="Column19" id="19"/>
+    <tableColumn name="Column20" id="20"/>
+    <tableColumn name="Column21" id="21"/>
+    <tableColumn name="Column22" id="22"/>
+    <tableColumn name="Column23" id="23"/>
+    <tableColumn name="Column24" id="24"/>
+    <tableColumn name="Column25" id="25"/>
+    <tableColumn name="Column26" id="26"/>
+    <tableColumn name="Column27" id="27"/>
+    <tableColumn name="Column28" id="28"/>
+    <tableColumn name="Column29" id="29"/>
+    <tableColumn name="Column30" id="30"/>
+    <tableColumn name="Column31" id="31"/>
+    <tableColumn name="Column32" id="32"/>
+    <tableColumn name="Column33" id="33"/>
+    <tableColumn name="Column34" id="34"/>
+    <tableColumn name="Column35" id="35"/>
+    <tableColumn name="Column36" id="36"/>
+    <tableColumn name="Column37" id="37"/>
+    <tableColumn name="Column38" id="38"/>
+    <tableColumn name="Column39" id="39"/>
+    <tableColumn name="Column40" id="40"/>
+    <tableColumn name="Column41" id="41"/>
+    <tableColumn name="Column42" id="42"/>
+    <tableColumn name="Column43" id="43"/>
+    <tableColumn name="Column44" id="44"/>
+    <tableColumn name="Column45" id="45"/>
+    <tableColumn name="Column46" id="46"/>
+    <tableColumn name="Column47" id="47"/>
+    <tableColumn name="Column48" id="48"/>
+    <tableColumn name="Column49" id="49"/>
+    <tableColumn name="Column50" id="50"/>
+    <tableColumn name="Column51" id="51"/>
+    <tableColumn name="Column52" id="52"/>
+    <tableColumn name="Column53" id="53"/>
+    <tableColumn name="Column54" id="54"/>
+    <tableColumn name="Column55" id="55"/>
+    <tableColumn name="Column56" id="56"/>
+    <tableColumn name="Column57" id="57"/>
+    <tableColumn name="Column58" id="58"/>
+    <tableColumn name="Column59" id="59"/>
+    <tableColumn name="Column60" id="60"/>
+    <tableColumn name="Column61" id="61"/>
+    <tableColumn name="Column62" id="62"/>
+    <tableColumn name="Column63" id="63"/>
+    <tableColumn name="Column64" id="64"/>
+    <tableColumn name="Column65" id="65"/>
+    <tableColumn name="Column66" id="66"/>
+    <tableColumn name="Column67" id="67"/>
+    <tableColumn name="Column68" id="68"/>
+    <tableColumn name="Column69" id="69"/>
+    <tableColumn name="Column70" id="70"/>
+    <tableColumn name="Column71" id="71"/>
+    <tableColumn name="Column72" id="72"/>
+    <tableColumn name="Column73" id="73"/>
+    <tableColumn name="Column74" id="74"/>
+    <tableColumn name="Column75" id="75"/>
+    <tableColumn name="Column76" id="76"/>
+    <tableColumn name="Column77" id="77"/>
+    <tableColumn name="Column78" id="78"/>
+    <tableColumn name="Column79" id="79"/>
+    <tableColumn name="Column80" id="80"/>
+    <tableColumn name="Column81" id="81"/>
+    <tableColumn name="Column82" id="82"/>
+    <tableColumn name="Column83" id="83"/>
+    <tableColumn name="Column84" id="84"/>
+    <tableColumn name="Column85" id="85"/>
+    <tableColumn name="Column86" id="86"/>
+    <tableColumn name="Column87" id="87"/>
+    <tableColumn name="Column88" id="88"/>
+    <tableColumn name="Column89" id="89"/>
+    <tableColumn name="Column90" id="90"/>
+    <tableColumn name="Column91" id="91"/>
+    <tableColumn name="Column92" id="92"/>
+    <tableColumn name="Column93" id="93"/>
+    <tableColumn name="Column94" id="94"/>
+    <tableColumn name="Column95" id="95"/>
+    <tableColumn name="Column96" id="96"/>
+    <tableColumn name="Column97" id="97"/>
+    <tableColumn name="Column98" id="98"/>
+    <tableColumn name="Column99" id="99"/>
+    <tableColumn name="Column100" id="100"/>
+    <tableColumn name="Column101" id="101"/>
+    <tableColumn name="Column102" id="102"/>
+    <tableColumn name="Column103" id="103"/>
+    <tableColumn name="Column104" id="104"/>
+    <tableColumn name="Column105" id="105"/>
+    <tableColumn name="Column106" id="106"/>
+    <tableColumn name="Column107" id="107"/>
+    <tableColumn name="Column108" id="108"/>
+    <tableColumn name="Column109" id="109"/>
+    <tableColumn name="Column110" id="110"/>
+    <tableColumn name="Column111" id="111"/>
+    <tableColumn name="Column112" id="112"/>
+  </tableColumns>
+  <tableStyleInfo name="Form responses 1-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -4015,6 +4417,1320 @@
         <v>14.98</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="11">
+        <v>46137.48536798611</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="14"/>
+      <c r="O56" s="14"/>
+      <c r="P56" s="14"/>
+      <c r="Q56" s="14"/>
+      <c r="R56" s="14"/>
+      <c r="S56" s="14"/>
+      <c r="T56" s="14"/>
+      <c r="U56" s="14"/>
+      <c r="V56" s="14"/>
+      <c r="W56" s="14"/>
+      <c r="X56" s="14"/>
+      <c r="Y56" s="14"/>
+      <c r="Z56" s="14"/>
+      <c r="AA56" s="14"/>
+      <c r="AB56" s="14"/>
+      <c r="AC56" s="14"/>
+      <c r="AD56" s="14"/>
+      <c r="AE56" s="14"/>
+      <c r="AF56" s="14"/>
+      <c r="AG56" s="14"/>
+      <c r="AH56" s="14"/>
+      <c r="AI56" s="14"/>
+      <c r="AJ56" s="14"/>
+      <c r="AK56" s="14"/>
+      <c r="AL56" s="14"/>
+      <c r="AM56" s="14"/>
+      <c r="AN56" s="14"/>
+      <c r="AO56" s="14"/>
+      <c r="AP56" s="14"/>
+      <c r="AQ56" s="14"/>
+      <c r="AR56" s="14"/>
+      <c r="AS56" s="14"/>
+      <c r="AT56" s="14"/>
+      <c r="AU56" s="14"/>
+      <c r="AV56" s="14"/>
+      <c r="AW56" s="14"/>
+      <c r="AX56" s="14"/>
+      <c r="AY56" s="14"/>
+      <c r="AZ56" s="14"/>
+      <c r="BA56" s="14"/>
+      <c r="BB56" s="14"/>
+      <c r="BC56" s="14"/>
+      <c r="BD56" s="14"/>
+      <c r="BE56" s="14"/>
+      <c r="BF56" s="14"/>
+      <c r="BG56" s="14"/>
+      <c r="BH56" s="14"/>
+      <c r="BI56" s="14"/>
+      <c r="BJ56" s="14"/>
+      <c r="BK56" s="14"/>
+      <c r="BL56" s="14"/>
+      <c r="BM56" s="14"/>
+      <c r="BN56" s="14"/>
+      <c r="BO56" s="14"/>
+      <c r="BP56" s="14"/>
+      <c r="BQ56" s="14"/>
+      <c r="BR56" s="14"/>
+      <c r="BS56" s="14"/>
+      <c r="BT56" s="14"/>
+      <c r="BU56" s="14"/>
+      <c r="BV56" s="14"/>
+      <c r="BW56" s="14"/>
+      <c r="BX56" s="14"/>
+      <c r="BY56" s="14"/>
+      <c r="BZ56" s="14"/>
+      <c r="CA56" s="14"/>
+      <c r="CB56" s="14"/>
+      <c r="CC56" s="15">
+        <v>10.91</v>
+      </c>
+      <c r="CD56" s="15">
+        <v>11.24</v>
+      </c>
+      <c r="CE56" s="15">
+        <v>10.03</v>
+      </c>
+      <c r="CF56" s="15">
+        <v>10.67</v>
+      </c>
+      <c r="CG56" s="15">
+        <v>17.88</v>
+      </c>
+      <c r="CH56" s="15">
+        <v>10.03</v>
+      </c>
+      <c r="CI56" s="15">
+        <v>10.94</v>
+      </c>
+      <c r="CJ56" s="14"/>
+      <c r="CK56" s="14"/>
+      <c r="CL56" s="14"/>
+      <c r="CM56" s="14"/>
+      <c r="CN56" s="14"/>
+      <c r="CO56" s="14"/>
+      <c r="CP56" s="14"/>
+      <c r="CQ56" s="14"/>
+      <c r="CR56" s="14"/>
+      <c r="CS56" s="14"/>
+      <c r="CT56" s="14"/>
+      <c r="CU56" s="14"/>
+      <c r="CV56" s="14"/>
+      <c r="CW56" s="14"/>
+      <c r="CX56" s="14"/>
+      <c r="CY56" s="14"/>
+      <c r="CZ56" s="14"/>
+      <c r="DA56" s="14"/>
+      <c r="DB56" s="14"/>
+      <c r="DC56" s="14"/>
+      <c r="DD56" s="14"/>
+      <c r="DE56" s="14"/>
+      <c r="DF56" s="14"/>
+      <c r="DG56" s="14"/>
+      <c r="DH56" s="16"/>
+      <c r="DI56" s="17"/>
+      <c r="DJ56" s="17"/>
+      <c r="DK56" s="17"/>
+      <c r="DL56" s="17"/>
+      <c r="DM56" s="17"/>
+      <c r="DN56" s="17"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="18">
+        <v>46137.511978043985</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="F57" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="21"/>
+      <c r="K57" s="21"/>
+      <c r="L57" s="21"/>
+      <c r="M57" s="21"/>
+      <c r="N57" s="21"/>
+      <c r="O57" s="21"/>
+      <c r="P57" s="21"/>
+      <c r="Q57" s="21"/>
+      <c r="R57" s="21"/>
+      <c r="S57" s="21"/>
+      <c r="T57" s="21"/>
+      <c r="U57" s="21"/>
+      <c r="V57" s="21"/>
+      <c r="W57" s="21"/>
+      <c r="X57" s="21"/>
+      <c r="Y57" s="21"/>
+      <c r="Z57" s="21"/>
+      <c r="AA57" s="21"/>
+      <c r="AB57" s="21"/>
+      <c r="AC57" s="21"/>
+      <c r="AD57" s="21"/>
+      <c r="AE57" s="21"/>
+      <c r="AF57" s="21"/>
+      <c r="AG57" s="21"/>
+      <c r="AH57" s="21"/>
+      <c r="AI57" s="21"/>
+      <c r="AJ57" s="21"/>
+      <c r="AK57" s="21"/>
+      <c r="AL57" s="21"/>
+      <c r="AM57" s="21"/>
+      <c r="AN57" s="21"/>
+      <c r="AO57" s="21"/>
+      <c r="AP57" s="21"/>
+      <c r="AQ57" s="21"/>
+      <c r="AR57" s="21"/>
+      <c r="AS57" s="21"/>
+      <c r="AT57" s="22">
+        <v>39.02</v>
+      </c>
+      <c r="AU57" s="22">
+        <v>32.66</v>
+      </c>
+      <c r="AV57" s="22">
+        <v>50.49</v>
+      </c>
+      <c r="AW57" s="22">
+        <v>35.64</v>
+      </c>
+      <c r="AX57" s="22">
+        <v>54.15</v>
+      </c>
+      <c r="AY57" s="22">
+        <v>32.66</v>
+      </c>
+      <c r="AZ57" s="22">
+        <v>41.71</v>
+      </c>
+      <c r="BA57" s="21"/>
+      <c r="BB57" s="21"/>
+      <c r="BC57" s="21"/>
+      <c r="BD57" s="21"/>
+      <c r="BE57" s="21"/>
+      <c r="BF57" s="21"/>
+      <c r="BG57" s="21"/>
+      <c r="BH57" s="21"/>
+      <c r="BI57" s="21"/>
+      <c r="BJ57" s="21"/>
+      <c r="BK57" s="21"/>
+      <c r="BL57" s="21"/>
+      <c r="BM57" s="21"/>
+      <c r="BN57" s="21"/>
+      <c r="BO57" s="21"/>
+      <c r="BP57" s="21"/>
+      <c r="BQ57" s="21"/>
+      <c r="BR57" s="21"/>
+      <c r="BS57" s="21"/>
+      <c r="BT57" s="21"/>
+      <c r="BU57" s="21"/>
+      <c r="BV57" s="21"/>
+      <c r="BW57" s="21"/>
+      <c r="BX57" s="21"/>
+      <c r="BY57" s="21"/>
+      <c r="BZ57" s="21"/>
+      <c r="CA57" s="21"/>
+      <c r="CB57" s="21"/>
+      <c r="CC57" s="21"/>
+      <c r="CD57" s="21"/>
+      <c r="CE57" s="21"/>
+      <c r="CF57" s="21"/>
+      <c r="CG57" s="21"/>
+      <c r="CH57" s="21"/>
+      <c r="CI57" s="21"/>
+      <c r="CJ57" s="21"/>
+      <c r="CK57" s="21"/>
+      <c r="CL57" s="21"/>
+      <c r="CM57" s="21"/>
+      <c r="CN57" s="21"/>
+      <c r="CO57" s="21"/>
+      <c r="CP57" s="21"/>
+      <c r="CQ57" s="21"/>
+      <c r="CR57" s="21"/>
+      <c r="CS57" s="21"/>
+      <c r="CT57" s="21"/>
+      <c r="CU57" s="21"/>
+      <c r="CV57" s="21"/>
+      <c r="CW57" s="21"/>
+      <c r="CX57" s="21"/>
+      <c r="CY57" s="21"/>
+      <c r="CZ57" s="21"/>
+      <c r="DA57" s="21"/>
+      <c r="DB57" s="21"/>
+      <c r="DC57" s="21"/>
+      <c r="DD57" s="21"/>
+      <c r="DE57" s="21"/>
+      <c r="DF57" s="21"/>
+      <c r="DG57" s="21"/>
+      <c r="DH57" s="23"/>
+      <c r="DI57" s="17"/>
+      <c r="DJ57" s="17"/>
+      <c r="DK57" s="17"/>
+      <c r="DL57" s="17"/>
+      <c r="DM57" s="17"/>
+      <c r="DN57" s="17"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="11">
+        <v>46137.54377375</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F58" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
+      <c r="M58" s="14"/>
+      <c r="N58" s="14"/>
+      <c r="O58" s="15">
+        <v>24.84</v>
+      </c>
+      <c r="P58" s="15">
+        <v>24.63</v>
+      </c>
+      <c r="Q58" s="15">
+        <v>29.23</v>
+      </c>
+      <c r="R58" s="15">
+        <v>22.49</v>
+      </c>
+      <c r="S58" s="15">
+        <v>21.4</v>
+      </c>
+      <c r="T58" s="15">
+        <v>21.4</v>
+      </c>
+      <c r="U58" s="15">
+        <v>23.98</v>
+      </c>
+      <c r="V58" s="14"/>
+      <c r="W58" s="14"/>
+      <c r="X58" s="14"/>
+      <c r="Y58" s="14"/>
+      <c r="Z58" s="14"/>
+      <c r="AA58" s="14"/>
+      <c r="AB58" s="14"/>
+      <c r="AC58" s="14"/>
+      <c r="AD58" s="14"/>
+      <c r="AE58" s="14"/>
+      <c r="AF58" s="14"/>
+      <c r="AG58" s="14"/>
+      <c r="AH58" s="14"/>
+      <c r="AI58" s="14"/>
+      <c r="AJ58" s="14"/>
+      <c r="AK58" s="14"/>
+      <c r="AL58" s="14"/>
+      <c r="AM58" s="14"/>
+      <c r="AN58" s="14"/>
+      <c r="AO58" s="14"/>
+      <c r="AP58" s="14"/>
+      <c r="AQ58" s="14"/>
+      <c r="AR58" s="14"/>
+      <c r="AS58" s="14"/>
+      <c r="AT58" s="14"/>
+      <c r="AU58" s="14"/>
+      <c r="AV58" s="14"/>
+      <c r="AW58" s="14"/>
+      <c r="AX58" s="14"/>
+      <c r="AY58" s="14"/>
+      <c r="AZ58" s="14"/>
+      <c r="BA58" s="14"/>
+      <c r="BB58" s="14"/>
+      <c r="BC58" s="14"/>
+      <c r="BD58" s="14"/>
+      <c r="BE58" s="14"/>
+      <c r="BF58" s="14"/>
+      <c r="BG58" s="14"/>
+      <c r="BH58" s="14"/>
+      <c r="BI58" s="14"/>
+      <c r="BJ58" s="14"/>
+      <c r="BK58" s="14"/>
+      <c r="BL58" s="14"/>
+      <c r="BM58" s="14"/>
+      <c r="BN58" s="14"/>
+      <c r="BO58" s="14"/>
+      <c r="BP58" s="14"/>
+      <c r="BQ58" s="14"/>
+      <c r="BR58" s="14"/>
+      <c r="BS58" s="14"/>
+      <c r="BT58" s="14"/>
+      <c r="BU58" s="14"/>
+      <c r="BV58" s="14"/>
+      <c r="BW58" s="14"/>
+      <c r="BX58" s="14"/>
+      <c r="BY58" s="14"/>
+      <c r="BZ58" s="14"/>
+      <c r="CA58" s="14"/>
+      <c r="CB58" s="14"/>
+      <c r="CC58" s="14"/>
+      <c r="CD58" s="14"/>
+      <c r="CE58" s="14"/>
+      <c r="CF58" s="14"/>
+      <c r="CG58" s="14"/>
+      <c r="CH58" s="14"/>
+      <c r="CI58" s="14"/>
+      <c r="CJ58" s="14"/>
+      <c r="CK58" s="14"/>
+      <c r="CL58" s="14"/>
+      <c r="CM58" s="14"/>
+      <c r="CN58" s="14"/>
+      <c r="CO58" s="14"/>
+      <c r="CP58" s="14"/>
+      <c r="CQ58" s="14"/>
+      <c r="CR58" s="14"/>
+      <c r="CS58" s="14"/>
+      <c r="CT58" s="14"/>
+      <c r="CU58" s="14"/>
+      <c r="CV58" s="14"/>
+      <c r="CW58" s="14"/>
+      <c r="CX58" s="14"/>
+      <c r="CY58" s="14"/>
+      <c r="CZ58" s="14"/>
+      <c r="DA58" s="14"/>
+      <c r="DB58" s="14"/>
+      <c r="DC58" s="14"/>
+      <c r="DD58" s="14"/>
+      <c r="DE58" s="14"/>
+      <c r="DF58" s="14"/>
+      <c r="DG58" s="14"/>
+      <c r="DH58" s="16"/>
+      <c r="DI58" s="17"/>
+      <c r="DJ58" s="17"/>
+      <c r="DK58" s="17"/>
+      <c r="DL58" s="17"/>
+      <c r="DM58" s="17"/>
+      <c r="DN58" s="17"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="18">
+        <v>46137.55896219907</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F59" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="G59" s="21"/>
+      <c r="H59" s="22">
+        <v>7.53</v>
+      </c>
+      <c r="I59" s="22">
+        <v>7.81</v>
+      </c>
+      <c r="J59" s="22">
+        <v>7.89</v>
+      </c>
+      <c r="K59" s="22">
+        <v>9.6</v>
+      </c>
+      <c r="L59" s="22">
+        <v>9.21</v>
+      </c>
+      <c r="M59" s="22">
+        <v>7.53</v>
+      </c>
+      <c r="N59" s="22">
+        <v>8.3</v>
+      </c>
+      <c r="O59" s="21"/>
+      <c r="P59" s="21"/>
+      <c r="Q59" s="21"/>
+      <c r="R59" s="21"/>
+      <c r="S59" s="21"/>
+      <c r="T59" s="21"/>
+      <c r="U59" s="21"/>
+      <c r="V59" s="21"/>
+      <c r="W59" s="21"/>
+      <c r="X59" s="21"/>
+      <c r="Y59" s="21"/>
+      <c r="Z59" s="21"/>
+      <c r="AA59" s="21"/>
+      <c r="AB59" s="21"/>
+      <c r="AC59" s="21"/>
+      <c r="AD59" s="21"/>
+      <c r="AE59" s="21"/>
+      <c r="AF59" s="21"/>
+      <c r="AG59" s="21"/>
+      <c r="AH59" s="21"/>
+      <c r="AI59" s="21"/>
+      <c r="AJ59" s="21"/>
+      <c r="AK59" s="21"/>
+      <c r="AL59" s="21"/>
+      <c r="AM59" s="21"/>
+      <c r="AN59" s="21"/>
+      <c r="AO59" s="21"/>
+      <c r="AP59" s="21"/>
+      <c r="AQ59" s="21"/>
+      <c r="AR59" s="21"/>
+      <c r="AS59" s="21"/>
+      <c r="AT59" s="21"/>
+      <c r="AU59" s="21"/>
+      <c r="AV59" s="21"/>
+      <c r="AW59" s="21"/>
+      <c r="AX59" s="21"/>
+      <c r="AY59" s="21"/>
+      <c r="AZ59" s="21"/>
+      <c r="BA59" s="21"/>
+      <c r="BB59" s="21"/>
+      <c r="BC59" s="21"/>
+      <c r="BD59" s="21"/>
+      <c r="BE59" s="21"/>
+      <c r="BF59" s="21"/>
+      <c r="BG59" s="21"/>
+      <c r="BH59" s="21"/>
+      <c r="BI59" s="21"/>
+      <c r="BJ59" s="21"/>
+      <c r="BK59" s="21"/>
+      <c r="BL59" s="21"/>
+      <c r="BM59" s="21"/>
+      <c r="BN59" s="21"/>
+      <c r="BO59" s="21"/>
+      <c r="BP59" s="21"/>
+      <c r="BQ59" s="21"/>
+      <c r="BR59" s="21"/>
+      <c r="BS59" s="21"/>
+      <c r="BT59" s="21"/>
+      <c r="BU59" s="21"/>
+      <c r="BV59" s="21"/>
+      <c r="BW59" s="21"/>
+      <c r="BX59" s="21"/>
+      <c r="BY59" s="21"/>
+      <c r="BZ59" s="21"/>
+      <c r="CA59" s="21"/>
+      <c r="CB59" s="21"/>
+      <c r="CC59" s="21"/>
+      <c r="CD59" s="21"/>
+      <c r="CE59" s="21"/>
+      <c r="CF59" s="21"/>
+      <c r="CG59" s="21"/>
+      <c r="CH59" s="21"/>
+      <c r="CI59" s="21"/>
+      <c r="CJ59" s="21"/>
+      <c r="CK59" s="21"/>
+      <c r="CL59" s="21"/>
+      <c r="CM59" s="21"/>
+      <c r="CN59" s="21"/>
+      <c r="CO59" s="21"/>
+      <c r="CP59" s="21"/>
+      <c r="CQ59" s="21"/>
+      <c r="CR59" s="21"/>
+      <c r="CS59" s="21"/>
+      <c r="CT59" s="21"/>
+      <c r="CU59" s="21"/>
+      <c r="CV59" s="21"/>
+      <c r="CW59" s="21"/>
+      <c r="CX59" s="21"/>
+      <c r="CY59" s="21"/>
+      <c r="CZ59" s="21"/>
+      <c r="DA59" s="21"/>
+      <c r="DB59" s="21"/>
+      <c r="DC59" s="21"/>
+      <c r="DD59" s="21"/>
+      <c r="DE59" s="21"/>
+      <c r="DF59" s="21"/>
+      <c r="DG59" s="21"/>
+      <c r="DH59" s="23"/>
+      <c r="DI59" s="17"/>
+      <c r="DJ59" s="17"/>
+      <c r="DK59" s="17"/>
+      <c r="DL59" s="17"/>
+      <c r="DM59" s="17"/>
+      <c r="DN59" s="17"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11">
+        <v>46137.58721196759</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+      <c r="M60" s="14"/>
+      <c r="N60" s="14"/>
+      <c r="O60" s="14"/>
+      <c r="P60" s="14"/>
+      <c r="Q60" s="14"/>
+      <c r="R60" s="14"/>
+      <c r="S60" s="14"/>
+      <c r="T60" s="14"/>
+      <c r="U60" s="14"/>
+      <c r="V60" s="14"/>
+      <c r="W60" s="14"/>
+      <c r="X60" s="14"/>
+      <c r="Y60" s="14"/>
+      <c r="Z60" s="14"/>
+      <c r="AA60" s="14"/>
+      <c r="AB60" s="14"/>
+      <c r="AC60" s="14"/>
+      <c r="AD60" s="14"/>
+      <c r="AE60" s="14"/>
+      <c r="AF60" s="14"/>
+      <c r="AG60" s="14"/>
+      <c r="AH60" s="14"/>
+      <c r="AI60" s="14"/>
+      <c r="AJ60" s="14"/>
+      <c r="AK60" s="14"/>
+      <c r="AL60" s="14"/>
+      <c r="AM60" s="14"/>
+      <c r="AN60" s="14"/>
+      <c r="AO60" s="14"/>
+      <c r="AP60" s="14"/>
+      <c r="AQ60" s="14"/>
+      <c r="AR60" s="14"/>
+      <c r="AS60" s="14"/>
+      <c r="AT60" s="14"/>
+      <c r="AU60" s="14"/>
+      <c r="AV60" s="14"/>
+      <c r="AW60" s="14"/>
+      <c r="AX60" s="14"/>
+      <c r="AY60" s="14"/>
+      <c r="AZ60" s="14"/>
+      <c r="BA60" s="14"/>
+      <c r="BB60" s="14"/>
+      <c r="BC60" s="14"/>
+      <c r="BD60" s="14"/>
+      <c r="BE60" s="14"/>
+      <c r="BF60" s="14"/>
+      <c r="BG60" s="14"/>
+      <c r="BH60" s="14"/>
+      <c r="BI60" s="14"/>
+      <c r="BJ60" s="14"/>
+      <c r="BK60" s="14"/>
+      <c r="BL60" s="14"/>
+      <c r="BM60" s="14"/>
+      <c r="BN60" s="14"/>
+      <c r="BO60" s="15">
+        <v>8.57</v>
+      </c>
+      <c r="BP60" s="15">
+        <v>10.2</v>
+      </c>
+      <c r="BQ60" s="15">
+        <v>8.32</v>
+      </c>
+      <c r="BR60" s="15">
+        <v>8.57</v>
+      </c>
+      <c r="BS60" s="15">
+        <v>8.2</v>
+      </c>
+      <c r="BT60" s="15">
+        <v>8.2</v>
+      </c>
+      <c r="BU60" s="15">
+        <v>8.48</v>
+      </c>
+      <c r="BV60" s="14"/>
+      <c r="BW60" s="14"/>
+      <c r="BX60" s="14"/>
+      <c r="BY60" s="14"/>
+      <c r="BZ60" s="14"/>
+      <c r="CA60" s="14"/>
+      <c r="CB60" s="14"/>
+      <c r="CC60" s="14"/>
+      <c r="CD60" s="14"/>
+      <c r="CE60" s="14"/>
+      <c r="CF60" s="14"/>
+      <c r="CG60" s="14"/>
+      <c r="CH60" s="14"/>
+      <c r="CI60" s="14"/>
+      <c r="CJ60" s="14"/>
+      <c r="CK60" s="14"/>
+      <c r="CL60" s="14"/>
+      <c r="CM60" s="14"/>
+      <c r="CN60" s="14"/>
+      <c r="CO60" s="14"/>
+      <c r="CP60" s="14"/>
+      <c r="CQ60" s="14"/>
+      <c r="CR60" s="14"/>
+      <c r="CS60" s="14"/>
+      <c r="CT60" s="14"/>
+      <c r="CU60" s="14"/>
+      <c r="CV60" s="14"/>
+      <c r="CW60" s="14"/>
+      <c r="CX60" s="14"/>
+      <c r="CY60" s="14"/>
+      <c r="CZ60" s="14"/>
+      <c r="DA60" s="14"/>
+      <c r="DB60" s="14"/>
+      <c r="DC60" s="14"/>
+      <c r="DD60" s="14"/>
+      <c r="DE60" s="14"/>
+      <c r="DF60" s="14"/>
+      <c r="DG60" s="14"/>
+      <c r="DH60" s="16"/>
+      <c r="DI60" s="17"/>
+      <c r="DJ60" s="17"/>
+      <c r="DK60" s="17"/>
+      <c r="DL60" s="17"/>
+      <c r="DM60" s="17"/>
+      <c r="DN60" s="17"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="18">
+        <v>46137.60145256945</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="G61" s="21"/>
+      <c r="H61" s="21"/>
+      <c r="I61" s="21"/>
+      <c r="J61" s="21"/>
+      <c r="K61" s="21"/>
+      <c r="L61" s="21"/>
+      <c r="M61" s="21"/>
+      <c r="N61" s="21"/>
+      <c r="O61" s="21"/>
+      <c r="P61" s="21"/>
+      <c r="Q61" s="21"/>
+      <c r="R61" s="21"/>
+      <c r="S61" s="21"/>
+      <c r="T61" s="21"/>
+      <c r="U61" s="21"/>
+      <c r="V61" s="21"/>
+      <c r="W61" s="21"/>
+      <c r="X61" s="21"/>
+      <c r="Y61" s="21"/>
+      <c r="Z61" s="21"/>
+      <c r="AA61" s="21"/>
+      <c r="AB61" s="21"/>
+      <c r="AC61" s="21"/>
+      <c r="AD61" s="21"/>
+      <c r="AE61" s="21"/>
+      <c r="AF61" s="21"/>
+      <c r="AG61" s="21"/>
+      <c r="AH61" s="21"/>
+      <c r="AI61" s="21"/>
+      <c r="AJ61" s="21"/>
+      <c r="AK61" s="21"/>
+      <c r="AL61" s="21"/>
+      <c r="AM61" s="21"/>
+      <c r="AN61" s="21"/>
+      <c r="AO61" s="21"/>
+      <c r="AP61" s="21"/>
+      <c r="AQ61" s="21"/>
+      <c r="AR61" s="21"/>
+      <c r="AS61" s="21"/>
+      <c r="AT61" s="21"/>
+      <c r="AU61" s="21"/>
+      <c r="AV61" s="21"/>
+      <c r="AW61" s="21"/>
+      <c r="AX61" s="21"/>
+      <c r="AY61" s="21"/>
+      <c r="AZ61" s="21"/>
+      <c r="BA61" s="21"/>
+      <c r="BB61" s="21"/>
+      <c r="BC61" s="21"/>
+      <c r="BD61" s="21"/>
+      <c r="BE61" s="21"/>
+      <c r="BF61" s="21"/>
+      <c r="BG61" s="21"/>
+      <c r="BH61" s="22">
+        <v>10.96</v>
+      </c>
+      <c r="BI61" s="22">
+        <v>8.03</v>
+      </c>
+      <c r="BJ61" s="22">
+        <v>11.48</v>
+      </c>
+      <c r="BK61" s="22">
+        <v>8.33</v>
+      </c>
+      <c r="BL61" s="22">
+        <v>10.45</v>
+      </c>
+      <c r="BM61" s="22">
+        <v>8.03</v>
+      </c>
+      <c r="BN61" s="22">
+        <v>9.91</v>
+      </c>
+      <c r="BO61" s="21"/>
+      <c r="BP61" s="21"/>
+      <c r="BQ61" s="21"/>
+      <c r="BR61" s="21"/>
+      <c r="BS61" s="21"/>
+      <c r="BT61" s="21"/>
+      <c r="BU61" s="21"/>
+      <c r="BV61" s="21"/>
+      <c r="BW61" s="21"/>
+      <c r="BX61" s="21"/>
+      <c r="BY61" s="21"/>
+      <c r="BZ61" s="21"/>
+      <c r="CA61" s="21"/>
+      <c r="CB61" s="21"/>
+      <c r="CC61" s="21"/>
+      <c r="CD61" s="21"/>
+      <c r="CE61" s="21"/>
+      <c r="CF61" s="21"/>
+      <c r="CG61" s="21"/>
+      <c r="CH61" s="21"/>
+      <c r="CI61" s="21"/>
+      <c r="CJ61" s="21"/>
+      <c r="CK61" s="21"/>
+      <c r="CL61" s="21"/>
+      <c r="CM61" s="21"/>
+      <c r="CN61" s="21"/>
+      <c r="CO61" s="21"/>
+      <c r="CP61" s="21"/>
+      <c r="CQ61" s="21"/>
+      <c r="CR61" s="21"/>
+      <c r="CS61" s="21"/>
+      <c r="CT61" s="21"/>
+      <c r="CU61" s="21"/>
+      <c r="CV61" s="21"/>
+      <c r="CW61" s="21"/>
+      <c r="CX61" s="21"/>
+      <c r="CY61" s="21"/>
+      <c r="CZ61" s="21"/>
+      <c r="DA61" s="21"/>
+      <c r="DB61" s="21"/>
+      <c r="DC61" s="21"/>
+      <c r="DD61" s="21"/>
+      <c r="DE61" s="21"/>
+      <c r="DF61" s="21"/>
+      <c r="DG61" s="21"/>
+      <c r="DH61" s="23"/>
+      <c r="DI61" s="17"/>
+      <c r="DJ61" s="17"/>
+      <c r="DK61" s="17"/>
+      <c r="DL61" s="17"/>
+      <c r="DM61" s="17"/>
+      <c r="DN61" s="17"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11">
+        <v>46137.72467435185</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="14"/>
+      <c r="L62" s="14"/>
+      <c r="M62" s="14"/>
+      <c r="N62" s="14"/>
+      <c r="O62" s="14"/>
+      <c r="P62" s="14"/>
+      <c r="Q62" s="14"/>
+      <c r="R62" s="14"/>
+      <c r="S62" s="14"/>
+      <c r="T62" s="14"/>
+      <c r="U62" s="14"/>
+      <c r="V62" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="W62" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="X62" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="Y62" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z62" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA62" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="AB62" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="AC62" s="14"/>
+      <c r="AD62" s="14"/>
+      <c r="AE62" s="14"/>
+      <c r="AF62" s="14"/>
+      <c r="AG62" s="14"/>
+      <c r="AH62" s="14"/>
+      <c r="AI62" s="14"/>
+      <c r="AJ62" s="14"/>
+      <c r="AK62" s="14"/>
+      <c r="AL62" s="14"/>
+      <c r="AM62" s="14"/>
+      <c r="AN62" s="14"/>
+      <c r="AO62" s="14"/>
+      <c r="AP62" s="14"/>
+      <c r="AQ62" s="14"/>
+      <c r="AR62" s="14"/>
+      <c r="AS62" s="14"/>
+      <c r="AT62" s="14"/>
+      <c r="AU62" s="14"/>
+      <c r="AV62" s="14"/>
+      <c r="AW62" s="14"/>
+      <c r="AX62" s="14"/>
+      <c r="AY62" s="14"/>
+      <c r="AZ62" s="14"/>
+      <c r="BA62" s="14"/>
+      <c r="BB62" s="14"/>
+      <c r="BC62" s="14"/>
+      <c r="BD62" s="14"/>
+      <c r="BE62" s="14"/>
+      <c r="BF62" s="14"/>
+      <c r="BG62" s="14"/>
+      <c r="BH62" s="14"/>
+      <c r="BI62" s="14"/>
+      <c r="BJ62" s="14"/>
+      <c r="BK62" s="14"/>
+      <c r="BL62" s="14"/>
+      <c r="BM62" s="14"/>
+      <c r="BN62" s="14"/>
+      <c r="BO62" s="14"/>
+      <c r="BP62" s="14"/>
+      <c r="BQ62" s="14"/>
+      <c r="BR62" s="14"/>
+      <c r="BS62" s="14"/>
+      <c r="BT62" s="14"/>
+      <c r="BU62" s="14"/>
+      <c r="BV62" s="14"/>
+      <c r="BW62" s="14"/>
+      <c r="BX62" s="14"/>
+      <c r="BY62" s="14"/>
+      <c r="BZ62" s="14"/>
+      <c r="CA62" s="14"/>
+      <c r="CB62" s="14"/>
+      <c r="CC62" s="14"/>
+      <c r="CD62" s="14"/>
+      <c r="CE62" s="14"/>
+      <c r="CF62" s="14"/>
+      <c r="CG62" s="14"/>
+      <c r="CH62" s="14"/>
+      <c r="CI62" s="14"/>
+      <c r="CJ62" s="14"/>
+      <c r="CK62" s="14"/>
+      <c r="CL62" s="14"/>
+      <c r="CM62" s="14"/>
+      <c r="CN62" s="14"/>
+      <c r="CO62" s="14"/>
+      <c r="CP62" s="14"/>
+      <c r="CQ62" s="14"/>
+      <c r="CR62" s="14"/>
+      <c r="CS62" s="14"/>
+      <c r="CT62" s="14"/>
+      <c r="CU62" s="14"/>
+      <c r="CV62" s="14"/>
+      <c r="CW62" s="14"/>
+      <c r="CX62" s="14"/>
+      <c r="CY62" s="14"/>
+      <c r="CZ62" s="14"/>
+      <c r="DA62" s="14"/>
+      <c r="DB62" s="14"/>
+      <c r="DC62" s="14"/>
+      <c r="DD62" s="14"/>
+      <c r="DE62" s="14"/>
+      <c r="DF62" s="14"/>
+      <c r="DG62" s="14"/>
+      <c r="DH62" s="16"/>
+      <c r="DI62" s="17"/>
+      <c r="DJ62" s="17"/>
+      <c r="DK62" s="17"/>
+      <c r="DL62" s="17"/>
+      <c r="DM62" s="17"/>
+      <c r="DN62" s="17"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="18">
+        <v>46137.728024525466</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="F63" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="G63" s="21"/>
+      <c r="H63" s="21"/>
+      <c r="I63" s="21"/>
+      <c r="J63" s="21"/>
+      <c r="K63" s="21"/>
+      <c r="L63" s="21"/>
+      <c r="M63" s="21"/>
+      <c r="N63" s="21"/>
+      <c r="O63" s="21"/>
+      <c r="P63" s="21"/>
+      <c r="Q63" s="21"/>
+      <c r="R63" s="21"/>
+      <c r="S63" s="21"/>
+      <c r="T63" s="21"/>
+      <c r="U63" s="21"/>
+      <c r="V63" s="21"/>
+      <c r="W63" s="21"/>
+      <c r="X63" s="21"/>
+      <c r="Y63" s="21"/>
+      <c r="Z63" s="21"/>
+      <c r="AA63" s="21"/>
+      <c r="AB63" s="21"/>
+      <c r="AC63" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="AD63" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="AE63" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="AF63" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="AG63" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="AH63" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="AI63" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="AJ63" s="21"/>
+      <c r="AK63" s="21"/>
+      <c r="AL63" s="21"/>
+      <c r="AM63" s="21"/>
+      <c r="AN63" s="21"/>
+      <c r="AO63" s="21"/>
+      <c r="AP63" s="21"/>
+      <c r="AQ63" s="21"/>
+      <c r="AR63" s="21"/>
+      <c r="AS63" s="21"/>
+      <c r="AT63" s="21"/>
+      <c r="AU63" s="21"/>
+      <c r="AV63" s="21"/>
+      <c r="AW63" s="21"/>
+      <c r="AX63" s="21"/>
+      <c r="AY63" s="21"/>
+      <c r="AZ63" s="21"/>
+      <c r="BA63" s="21"/>
+      <c r="BB63" s="21"/>
+      <c r="BC63" s="21"/>
+      <c r="BD63" s="21"/>
+      <c r="BE63" s="21"/>
+      <c r="BF63" s="21"/>
+      <c r="BG63" s="21"/>
+      <c r="BH63" s="21"/>
+      <c r="BI63" s="21"/>
+      <c r="BJ63" s="21"/>
+      <c r="BK63" s="21"/>
+      <c r="BL63" s="21"/>
+      <c r="BM63" s="21"/>
+      <c r="BN63" s="21"/>
+      <c r="BO63" s="21"/>
+      <c r="BP63" s="21"/>
+      <c r="BQ63" s="21"/>
+      <c r="BR63" s="21"/>
+      <c r="BS63" s="21"/>
+      <c r="BT63" s="21"/>
+      <c r="BU63" s="21"/>
+      <c r="BV63" s="21"/>
+      <c r="BW63" s="21"/>
+      <c r="BX63" s="21"/>
+      <c r="BY63" s="21"/>
+      <c r="BZ63" s="21"/>
+      <c r="CA63" s="21"/>
+      <c r="CB63" s="21"/>
+      <c r="CC63" s="21"/>
+      <c r="CD63" s="21"/>
+      <c r="CE63" s="21"/>
+      <c r="CF63" s="21"/>
+      <c r="CG63" s="21"/>
+      <c r="CH63" s="21"/>
+      <c r="CI63" s="21"/>
+      <c r="CJ63" s="21"/>
+      <c r="CK63" s="21"/>
+      <c r="CL63" s="21"/>
+      <c r="CM63" s="21"/>
+      <c r="CN63" s="21"/>
+      <c r="CO63" s="21"/>
+      <c r="CP63" s="21"/>
+      <c r="CQ63" s="21"/>
+      <c r="CR63" s="21"/>
+      <c r="CS63" s="21"/>
+      <c r="CT63" s="21"/>
+      <c r="CU63" s="21"/>
+      <c r="CV63" s="21"/>
+      <c r="CW63" s="21"/>
+      <c r="CX63" s="21"/>
+      <c r="CY63" s="21"/>
+      <c r="CZ63" s="21"/>
+      <c r="DA63" s="21"/>
+      <c r="DB63" s="21"/>
+      <c r="DC63" s="21"/>
+      <c r="DD63" s="21"/>
+      <c r="DE63" s="21"/>
+      <c r="DF63" s="21"/>
+      <c r="DG63" s="21"/>
+      <c r="DH63" s="23"/>
+      <c r="DI63" s="17"/>
+      <c r="DJ63" s="17"/>
+      <c r="DK63" s="17"/>
+      <c r="DL63" s="17"/>
+      <c r="DM63" s="17"/>
+      <c r="DN63" s="17"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="24">
+        <v>46138.55581564815</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="D64" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="E64" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="F64" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="G64" s="27"/>
+      <c r="H64" s="27"/>
+      <c r="I64" s="27"/>
+      <c r="J64" s="27"/>
+      <c r="K64" s="27"/>
+      <c r="L64" s="27"/>
+      <c r="M64" s="27"/>
+      <c r="N64" s="27"/>
+      <c r="O64" s="27"/>
+      <c r="P64" s="27"/>
+      <c r="Q64" s="27"/>
+      <c r="R64" s="27"/>
+      <c r="S64" s="27"/>
+      <c r="T64" s="27"/>
+      <c r="U64" s="27"/>
+      <c r="V64" s="27"/>
+      <c r="W64" s="27"/>
+      <c r="X64" s="27"/>
+      <c r="Y64" s="27"/>
+      <c r="Z64" s="27"/>
+      <c r="AA64" s="27"/>
+      <c r="AB64" s="27"/>
+      <c r="AC64" s="27"/>
+      <c r="AD64" s="27"/>
+      <c r="AE64" s="27"/>
+      <c r="AF64" s="27"/>
+      <c r="AG64" s="27"/>
+      <c r="AH64" s="27"/>
+      <c r="AI64" s="27"/>
+      <c r="AJ64" s="27"/>
+      <c r="AK64" s="27"/>
+      <c r="AL64" s="27"/>
+      <c r="AM64" s="27"/>
+      <c r="AN64" s="27"/>
+      <c r="AO64" s="27"/>
+      <c r="AP64" s="27"/>
+      <c r="AQ64" s="27"/>
+      <c r="AR64" s="27"/>
+      <c r="AS64" s="27"/>
+      <c r="AT64" s="27"/>
+      <c r="AU64" s="27"/>
+      <c r="AV64" s="27"/>
+      <c r="AW64" s="27"/>
+      <c r="AX64" s="27"/>
+      <c r="AY64" s="27"/>
+      <c r="AZ64" s="27"/>
+      <c r="BA64" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="BB64" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="BC64" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="BD64" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="BE64" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="BF64" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="BG64" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="BH64" s="27"/>
+      <c r="BI64" s="27"/>
+      <c r="BJ64" s="27"/>
+      <c r="BK64" s="27"/>
+      <c r="BL64" s="27"/>
+      <c r="BM64" s="27"/>
+      <c r="BN64" s="27"/>
+      <c r="BO64" s="27"/>
+      <c r="BP64" s="27"/>
+      <c r="BQ64" s="27"/>
+      <c r="BR64" s="27"/>
+      <c r="BS64" s="27"/>
+      <c r="BT64" s="27"/>
+      <c r="BU64" s="27"/>
+      <c r="BV64" s="27"/>
+      <c r="BW64" s="27"/>
+      <c r="BX64" s="27"/>
+      <c r="BY64" s="27"/>
+      <c r="BZ64" s="27"/>
+      <c r="CA64" s="27"/>
+      <c r="CB64" s="27"/>
+      <c r="CC64" s="27"/>
+      <c r="CD64" s="27"/>
+      <c r="CE64" s="27"/>
+      <c r="CF64" s="27"/>
+      <c r="CG64" s="27"/>
+      <c r="CH64" s="27"/>
+      <c r="CI64" s="27"/>
+      <c r="CJ64" s="27"/>
+      <c r="CK64" s="27"/>
+      <c r="CL64" s="27"/>
+      <c r="CM64" s="27"/>
+      <c r="CN64" s="27"/>
+      <c r="CO64" s="27"/>
+      <c r="CP64" s="27"/>
+      <c r="CQ64" s="27"/>
+      <c r="CR64" s="27"/>
+      <c r="CS64" s="27"/>
+      <c r="CT64" s="27"/>
+      <c r="CU64" s="27"/>
+      <c r="CV64" s="27"/>
+      <c r="CW64" s="27"/>
+      <c r="CX64" s="27"/>
+      <c r="CY64" s="27"/>
+      <c r="CZ64" s="27"/>
+      <c r="DA64" s="27"/>
+      <c r="DB64" s="27"/>
+      <c r="DC64" s="27"/>
+      <c r="DD64" s="27"/>
+      <c r="DE64" s="27"/>
+      <c r="DF64" s="27"/>
+      <c r="DG64" s="27"/>
+      <c r="DH64" s="28"/>
+      <c r="DI64" s="17"/>
+      <c r="DJ64" s="17"/>
+      <c r="DK64" s="17"/>
+      <c r="DL64" s="17"/>
+      <c r="DM64" s="17"/>
+      <c r="DN64" s="17"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="F2"/>
@@ -4071,10 +5787,20 @@
     <hyperlink r:id="rId52" ref="F53"/>
     <hyperlink r:id="rId53" ref="F54"/>
     <hyperlink r:id="rId54" ref="F55"/>
+    <hyperlink r:id="rId55" ref="F56"/>
+    <hyperlink r:id="rId56" ref="F57"/>
+    <hyperlink r:id="rId57" ref="F58"/>
+    <hyperlink r:id="rId58" ref="F59"/>
+    <hyperlink r:id="rId59" ref="F60"/>
+    <hyperlink r:id="rId60" ref="F61"/>
+    <hyperlink r:id="rId61" ref="F62"/>
+    <hyperlink r:id="rId62" ref="F63"/>
+    <hyperlink r:id="rId63" ref="F64"/>
   </hyperlinks>
-  <drawing r:id="rId55"/>
-  <tableParts count="1">
-    <tablePart r:id="rId57"/>
+  <drawing r:id="rId64"/>
+  <tableParts count="2">
+    <tablePart r:id="rId67"/>
+    <tablePart r:id="rId68"/>
   </tableParts>
 </worksheet>
 </file>